--- a/AAII_Financials/Yearly/CSTM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CSTM_YR_FIN.xlsx
@@ -3023,10 +3023,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>248000</v>
+        <v>224000</v>
       </c>
       <c r="E59" s="3">
-        <v>227000</v>
+        <v>205000</v>
       </c>
       <c r="F59" s="3">
         <v>239000</v>
